--- a/phase-01/management/RACI_сквозная.xlsx
+++ b/phase-01/management/RACI_сквозная.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E60D45-95AD-4231-9D29-28F162DFEEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RACI" sheetId="1" r:id="rId1"/>

--- a/phase-01/management/RACI_сквозная.xlsx
+++ b/phase-01/management/RACI_сквозная.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Works\VSU\ProjectManagment\phase-01\management\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vlaud Detect\Desktop\ProjectManagment\phase-01\management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E60D45-95AD-4231-9D29-28F162DFEEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9518872-5349-48FB-BE0C-A72BC6FB1465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RACI" sheetId="1" r:id="rId1"/>
@@ -18,19 +18,6 @@
     <sheet name="История изменений" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -316,9 +303,6 @@
     <t>Согласование</t>
   </si>
   <si>
-    <t>v1.0 (черновик)</t>
-  </si>
-  <si>
     <t>Перенесены T01–T15 из исходной книги; запись не подтверждает согласование команды.</t>
   </si>
   <si>
@@ -326,6 +310,9 @@
   </si>
   <si>
     <t>Ожидается</t>
+  </si>
+  <si>
+    <t>v1.0</t>
   </si>
 </sst>
 </file>
@@ -335,7 +322,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -367,10 +354,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF196E5D"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -406,38 +389,36 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -658,16 +639,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
     </row>
     <row r="3" spans="1:8" ht="36" customHeight="1">
       <c r="A3" s="8" t="s">
@@ -682,433 +663,433 @@
       <c r="H3" s="8"/>
     </row>
     <row r="5" spans="1:8" ht="31.95" customHeight="1">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="37.049999999999997" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="D6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="4" t="str">
+      <c r="G6" s="5" t="str">
         <f t="shared" ref="G6:G20" si="0">IF(COUNTIF(D6:F6,"A/R")+COUNTIF(D6:F6,"A")=1,"OK","ПРОВЕРИТЬ")</f>
         <v>OK</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="37.049999999999997" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="D7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="4" t="str">
+      <c r="G7" s="5" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="37.049999999999997" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="E8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="4" t="str">
+      <c r="G8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="37.049999999999997" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="4" t="str">
+      <c r="F9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="37.049999999999997" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="4" t="str">
+      <c r="F10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="37.049999999999997" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="A11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="D11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="4" t="str">
+      <c r="G11" s="5" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="37.049999999999997" customHeight="1">
-      <c r="A12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="A12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="E12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="4" t="str">
+      <c r="G12" s="5" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="37.049999999999997" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="3" t="s">
+      <c r="A13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="E13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G13" s="4" t="str">
+      <c r="G13" s="5" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="6" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="37.049999999999997" customHeight="1">
-      <c r="A14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="A14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="4" t="str">
+      <c r="F14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="5" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="37.049999999999997" customHeight="1">
-      <c r="A15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="A15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="4" t="str">
+      <c r="F15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="5" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="6" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="37.049999999999997" customHeight="1">
-      <c r="A16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="A16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="E16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="4" t="str">
+      <c r="G16" s="5" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="37.049999999999997" customHeight="1">
-      <c r="A17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="3" t="s">
+      <c r="A17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="D17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="4" t="str">
+      <c r="G17" s="5" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="6" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="37.049999999999997" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="A18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="D18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G18" s="4" t="str">
+      <c r="G18" s="5" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="6" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="37.049999999999997" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="3" t="s">
+      <c r="A19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="4" t="str">
+      <c r="F19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="5" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="6" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="37.049999999999997" customHeight="1">
-      <c r="A20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="3" t="s">
+      <c r="A20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="D20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G20" s="4" t="str">
+      <c r="G20" s="5" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="6" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1142,12 +1123,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26.4" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
     </row>
     <row r="3" spans="1:4" ht="28.8" customHeight="1">
       <c r="A3" s="8" t="s">
@@ -1158,106 +1139,106 @@
       <c r="D3" s="8"/>
     </row>
     <row r="5" spans="1:4" ht="25.65" customHeight="1">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="37.65" customHeight="1">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="37.65" customHeight="1">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="37.65" customHeight="1">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="37.65" customHeight="1">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="37.65" customHeight="1">
-      <c r="A10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="A10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="37.65" customHeight="1">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
     </row>
     <row r="12" spans="1:4" ht="56.4" customHeight="1">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1284,53 +1265,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="4" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="43.95" customHeight="1">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <v>46308</v>
       </c>
       <c r="B5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
